--- a/registration_forms/031_ai_predictive_modelling_workshop_registration_form--registration_forms.xlsx
+++ b/registration_forms/031_ai_predictive_modelling_workshop_registration_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -967,12 +967,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'python_(pandas,_scikit-learn,_etc.)',_'value':_'python'}</t>
+          <t>python_(pandas,_scikit-learn,_etc.)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Python (Pandas, Scikit-learn, etc.)', 'value': 'python'}</t>
+          <t>Python (Pandas, Scikit-learn, etc.)</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'r_(tidyverse,_caret,_etc.)',_'value':_'r_lang'}</t>
+          <t>r_(tidyverse,_caret,_etc.)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'R (Tidyverse, Caret, etc.)', 'value': 'r_lang'}</t>
+          <t>R (Tidyverse, Caret, etc.)</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'sql_(data_extraction)',_'value':_'sql'}</t>
+          <t>sql_(data_extraction)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'SQL (Data extraction)', 'value': 'sql'}</t>
+          <t>SQL (Data extraction)</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'sas_/_stata',_'value':_'legacy_stats'}</t>
+          <t>sas_/_stata</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'SAS / Stata', 'value': 'legacy_stats'}</t>
+          <t>SAS / Stata</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'none_/_excel_only',_'value':_'none'}</t>
+          <t>none_/_excel_only</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'None / Excel Only', 'value': 'none'}</t>
+          <t>None / Excel Only</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'beginner_(no_prior_experience)',_'value':_'beginner'}</t>
+          <t>beginner_(no_prior_experience)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Beginner (No prior experience)', 'value': 'beginner'}</t>
+          <t>Beginner (No prior experience)</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'basic_(understand_concepts,_run_basic_regressions)',_'value':_'basic'}</t>
+          <t>basic_(understand_concepts,_run_basic_regressions)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Basic (Understand concepts, run basic regressions)', 'value': 'basic'}</t>
+          <t>Basic (Understand concepts, run basic regressions)</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'intermediate_(built_and_deployed_models)',_'value':_'intermediate'}</t>
+          <t>intermediate_(built_and_deployed_models)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Intermediate (Built and deployed models)', 'value': 'intermediate'}</t>
+          <t>Intermediate (Built and deployed models)</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'advanced_(specialist_in_deep_learning/ensembles)',_'value':_'advanced'}</t>
+          <t>advanced_(specialist_in_deep_learning/ensembles)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Advanced (Specialist in deep learning/ensembles)', 'value': 'advanced'}</t>
+          <t>Advanced (Specialist in deep learning/ensembles)</t>
         </is>
       </c>
     </row>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'finance_/_insurance',_'value':_'finance'}</t>
+          <t>finance_/_insurance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Finance / Insurance', 'value': 'finance'}</t>
+          <t>Finance / Insurance</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'healthcare_/_pharmaceuticals',_'value':_'healthcare'}</t>
+          <t>healthcare_/_pharmaceuticals</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Healthcare / Pharmaceuticals', 'value': 'healthcare'}</t>
+          <t>Healthcare / Pharmaceuticals</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'retail_/_e-commerce',_'value':_'retail'}</t>
+          <t>retail_/_e-commerce</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Retail / E-commerce', 'value': 'retail'}</t>
+          <t>Retail / E-commerce</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'manufacturing_/_supply_chain',_'value':_'manufacturing'}</t>
+          <t>manufacturing_/_supply_chain</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Manufacturing / Supply Chain', 'value': 'manufacturing'}</t>
+          <t>Manufacturing / Supply Chain</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'energy_/_utilities',_'value':_'energy'}</t>
+          <t>energy_/_utilities</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Energy / Utilities', 'value': 'energy'}</t>
+          <t>Energy / Utilities</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'academic_research',_'value':_'research'}</t>
+          <t>academic_research</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Academic Research', 'value': 'research'}</t>
+          <t>Academic Research</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'august_20-21,_2026_(summer_intensive)',_'value':_'august_session'}</t>
+          <t>august_20-21,_2026_(summer_intensive)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'August 20-21, 2026 (Summer Intensive)', 'value': 'august_session'}</t>
+          <t>August 20-21, 2026 (Summer Intensive)</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'september_15-16,_2026_(fall_session)',_'value':_'september_session'}</t>
+          <t>september_15-16,_2026_(fall_session)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'September 15-16, 2026 (Fall Session)', 'value': 'september_session'}</t>
+          <t>September 15-16, 2026 (Fall Session)</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'hands-on_coding_(70%_code,_30%_theory)',_'value':_'coding_heavy'}</t>
+          <t>hands-on_coding_(70%_code,_30%_theory)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Hands-on Coding (70% Code, 30% Theory)', 'value': 'coding_heavy'}</t>
+          <t>Hands-on Coding (70% Code, 30% Theory)</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'theory_focused_(70%_concepts,_30%_examples)',_'value':_'theory_heavy'}</t>
+          <t>theory_focused_(70%_concepts,_30%_examples)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Theory Focused (70% Concepts, 30% Examples)', 'value': 'theory_heavy'}</t>
+          <t>Theory Focused (70% Concepts, 30% Examples)</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'balanced_(50/50)',_'value':_'balanced'}</t>
+          <t>balanced_(50/50)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Balanced (50/50)', 'value': 'balanced'}</t>
+          <t>Balanced (50/50)</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'time_series_forecasting',_'value':_'time_series'}</t>
+          <t>time_series_forecasting</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Time Series Forecasting', 'value': 'time_series'}</t>
+          <t>Time Series Forecasting</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'classification_&amp;_anomaly_detection',_'value':_'classification'}</t>
+          <t>classification_&amp;_anomaly_detection</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Classification &amp; Anomaly Detection', 'value': 'classification'}</t>
+          <t>Classification &amp; Anomaly Detection</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'feature_engineering_&amp;_selection',_'value':_'feature_eng'}</t>
+          <t>feature_engineering_&amp;_selection</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Feature Engineering &amp; Selection', 'value': 'feature_eng'}</t>
+          <t>Feature Engineering &amp; Selection</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'model_interpretation_(shap/lime)',_'value':_'interpretation'}</t>
+          <t>model_interpretation_(shap/lime)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Model Interpretation (SHAP/LIME)', 'value': 'interpretation'}</t>
+          <t>Model Interpretation (SHAP/LIME)</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_i_will_bring_my_own_device',_'value':_true}</t>
+          <t>yes,_i_will_bring_my_own_device</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, I will bring my own device', 'value': True}</t>
+          <t>Yes, I will bring my own device</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'no,_i_request_a_loaner_workstation',_'value':_false}</t>
+          <t>no,_i_request_a_loaner_workstation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'No, I request a loaner workstation', 'value': False}</t>
+          <t>No, I request a loaner workstation</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'credit_card',_'value':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Credit Card', 'value': 'credit_card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'paypal',_'value':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'PayPal', 'value': 'paypal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'corporate_po_/_invoice',_'value':_'invoice'}</t>
+          <t>corporate_po_/_invoice</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Corporate PO / Invoice', 'value': 'invoice'}</t>
+          <t>Corporate PO / Invoice</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
